--- a/table/resources/sample/mail.xlsx
+++ b/table/resources/sample/mail.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -212,6 +217,12 @@
   </si>
   <si>
     <t>您在【累计福利】活动中已完成累计任务挑战，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>买一送七</t>
+  </si>
+  <si>
+    <t>您在【买一送七】活动中还有未领取的奖励，请尽快领取!</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1274,7 +1285,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F31" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F32" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1980,6 +1991,33 @@
       </c>
       <c r="H31" s="3" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3">
+        <v>49</v>
+      </c>
+      <c r="B32" s="3">
+        <v>11634</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>11635</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
